--- a/Matricula_2do_grado.xlsx
+++ b/Matricula_2do_grado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2DD98B-019D-47EF-BF6C-815727AFE7F4}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C678BB5-75D4-4FF3-A873-30F584BDA933}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="278" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -428,6 +428,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -467,14 +474,6 @@
     <font>
       <b/>
       <sz val="14"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -686,127 +685,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -814,7 +706,7 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -829,14 +721,116 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1165,7 +1159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DB39836-5B3B-429B-9311-60F87BF15BBF}">
-  <dimension ref="A1:V32"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19.28515625" customWidth="1"/>
@@ -1181,7 +1175,7 @@
     <col min="22" max="22" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:29">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1205,7 +1199,7 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:29">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1229,7 +1223,7 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:29">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -1253,7 +1247,7 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:29">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1277,1304 +1271,1574 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
     </row>
-    <row r="5" spans="1:22" ht="20.25">
-      <c r="A5" s="25" t="s">
+    <row r="5" spans="1:29" ht="20.25">
+      <c r="A5" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="26"/>
-      <c r="R5" s="26"/>
-      <c r="S5" s="26"/>
-      <c r="T5" s="26"/>
-      <c r="U5" s="26"/>
-      <c r="V5" s="26"/>
-    </row>
-    <row r="6" spans="1:22">
-      <c r="A6" s="27" t="s">
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
+      <c r="Q5" s="46"/>
+      <c r="R5" s="46"/>
+      <c r="S5" s="46"/>
+      <c r="T5" s="46"/>
+      <c r="U5" s="46"/>
+      <c r="V5" s="46"/>
+    </row>
+    <row r="6" spans="1:29">
+      <c r="A6" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="27" t="s">
+      <c r="B6" s="44"/>
+      <c r="C6" s="42" t="s">
         <v>121</v>
       </c>
-      <c r="D6" s="28"/>
-      <c r="E6" s="27" t="s">
+      <c r="D6" s="44"/>
+      <c r="E6" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="27" t="s">
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="42" t="s">
         <v>123</v>
       </c>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="27" t="s">
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="27" t="s">
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="44"/>
+      <c r="Q6" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="R6" s="28"/>
-      <c r="S6" s="22" t="s">
+      <c r="R6" s="44"/>
+      <c r="S6" s="47" t="s">
         <v>125</v>
       </c>
-      <c r="T6" s="23"/>
-      <c r="U6" s="23"/>
-      <c r="V6" s="24"/>
-    </row>
-    <row r="7" spans="1:22" ht="42.75" customHeight="1">
-      <c r="A7" s="27" t="s">
+      <c r="T6" s="48"/>
+      <c r="U6" s="48"/>
+      <c r="V6" s="49"/>
+    </row>
+    <row r="7" spans="1:29" ht="42.75" customHeight="1">
+      <c r="A7" s="42" t="s">
         <v>126</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="28"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="44"/>
       <c r="D7" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="E7" s="31"/>
+      <c r="E7" s="32"/>
       <c r="F7" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="G7" s="31"/>
+      <c r="G7" s="32"/>
       <c r="H7" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="I7" s="32"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="27" t="s">
+      <c r="I7" s="31"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="42" t="s">
         <v>130</v>
       </c>
-      <c r="L7" s="28"/>
+      <c r="L7" s="44"/>
       <c r="M7" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="N7" s="31"/>
+      <c r="N7" s="32"/>
       <c r="O7" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="P7" s="32"/>
-      <c r="Q7" s="32"/>
-      <c r="R7" s="31"/>
-      <c r="S7" s="6" t="s">
+      <c r="P7" s="31"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="32"/>
+      <c r="S7" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="T7" s="6" t="s">
+      <c r="T7" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="U7" s="20" t="s">
+      <c r="U7" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="V7" s="21"/>
-    </row>
-    <row r="8" spans="1:22" ht="18">
-      <c r="A8" s="33" t="s">
+      <c r="V7" s="34"/>
+    </row>
+    <row r="8" spans="1:29" ht="18">
+      <c r="A8" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="33" t="s">
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="36"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="37"/>
+      <c r="Q8" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="R8" s="34"/>
-      <c r="S8" s="34"/>
-      <c r="T8" s="34"/>
-      <c r="U8" s="34"/>
-      <c r="V8" s="34"/>
-    </row>
-    <row r="9" spans="1:22">
-      <c r="A9" s="18" t="s">
+      <c r="R8" s="36"/>
+      <c r="S8" s="36"/>
+      <c r="T8" s="36"/>
+      <c r="U8" s="36"/>
+      <c r="V8" s="36"/>
+    </row>
+    <row r="9" spans="1:29">
+      <c r="A9" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="37"/>
-      <c r="F9" s="18" t="s">
+      <c r="E9" s="39"/>
+      <c r="F9" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="H9" s="38" t="s">
+      <c r="H9" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="I9" s="39"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="18" t="s">
+      <c r="I9" s="24"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="L9" s="38" t="s">
+      <c r="L9" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="M9" s="40"/>
-      <c r="N9" s="38" t="s">
+      <c r="M9" s="25"/>
+      <c r="N9" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="O9" s="39"/>
-      <c r="P9" s="40"/>
-      <c r="Q9" s="14" t="s">
+      <c r="O9" s="24"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="R9" s="15"/>
-      <c r="S9" s="18" t="s">
+      <c r="R9" s="27"/>
+      <c r="S9" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="T9" s="18" t="s">
+      <c r="T9" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="U9" s="18" t="s">
+      <c r="U9" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="V9" s="41" t="s">
+      <c r="V9" s="21" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="13" t="s">
+    <row r="10" spans="1:29">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="I10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="13" t="s">
+      <c r="J10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="19"/>
-      <c r="L10" s="13" t="s">
+      <c r="K10" s="20"/>
+      <c r="L10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="M10" s="13" t="s">
+      <c r="M10" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="N10" s="13" t="s">
+      <c r="N10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="O10" s="13" t="s">
+      <c r="O10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="P10" s="13" t="s">
+      <c r="P10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="17"/>
-      <c r="S10" s="19"/>
-      <c r="T10" s="19"/>
-      <c r="U10" s="19"/>
-      <c r="V10" s="44"/>
-    </row>
-    <row r="11" spans="1:22" ht="16.5">
+      <c r="Q10" s="28"/>
+      <c r="R10" s="29"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="22"/>
+    </row>
+    <row r="11" spans="1:29" ht="16.5">
       <c r="A11" s="2">
         <v>1</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="50">
         <v>11725560225</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="9" t="s">
+      <c r="C11" s="2"/>
+      <c r="D11" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="50" t="s">
         <v>62</v>
       </c>
       <c r="G11" s="2"/>
-      <c r="H11" s="46">
+      <c r="H11" s="9">
         <v>2</v>
       </c>
-      <c r="I11" s="46">
+      <c r="I11" s="9">
         <v>2</v>
       </c>
-      <c r="J11" s="45">
+      <c r="J11" s="8">
         <v>2018</v>
       </c>
-      <c r="K11" s="47" t="s">
+      <c r="K11" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="L11" s="47" t="s">
+      <c r="L11" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="M11" s="4"/>
-      <c r="N11" s="47">
+      <c r="M11" s="10"/>
+      <c r="N11" s="10">
         <v>10</v>
       </c>
-      <c r="O11" s="47">
+      <c r="O11" s="10">
         <v>10</v>
       </c>
-      <c r="P11" s="47">
+      <c r="P11" s="10">
         <v>36</v>
       </c>
-      <c r="Q11" s="52" t="s">
+      <c r="Q11" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="R11" s="52" t="s">
+      <c r="R11" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="S11" s="7">
+      <c r="S11" s="50">
         <v>25560225</v>
       </c>
-      <c r="T11" s="7">
+      <c r="T11" s="50">
         <v>4127244102</v>
       </c>
-      <c r="U11" s="7" t="s">
+      <c r="U11" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="V11" s="5" t="s">
+      <c r="V11" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" ht="16.5">
+      <c r="W11" s="52"/>
+      <c r="X11" s="52"/>
+      <c r="Y11" s="52"/>
+      <c r="Z11" s="52"/>
+      <c r="AA11" s="52"/>
+      <c r="AB11" s="52"/>
+      <c r="AC11" s="52"/>
+    </row>
+    <row r="12" spans="1:29" ht="16.5">
       <c r="A12" s="2">
         <v>2</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="50">
         <v>11811955345</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="9" t="s">
+      <c r="C12" s="2"/>
+      <c r="D12" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G12" s="2"/>
-      <c r="H12" s="46">
+      <c r="H12" s="9">
         <v>29</v>
       </c>
-      <c r="I12" s="46">
+      <c r="I12" s="9">
         <v>2</v>
       </c>
-      <c r="J12" s="45">
+      <c r="J12" s="8">
         <v>2018</v>
       </c>
-      <c r="K12" s="47" t="s">
+      <c r="K12" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="L12" s="47" t="s">
+      <c r="L12" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="M12" s="4"/>
-      <c r="N12" s="47">
+      <c r="M12" s="10"/>
+      <c r="N12" s="10">
         <v>12</v>
       </c>
-      <c r="O12" s="47">
+      <c r="O12" s="10">
         <v>12</v>
       </c>
-      <c r="P12" s="47">
+      <c r="P12" s="10">
         <v>35</v>
       </c>
-      <c r="Q12" s="52" t="s">
+      <c r="Q12" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="R12" s="52" t="s">
+      <c r="R12" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="S12" s="7">
+      <c r="S12" s="50">
         <v>11955345</v>
       </c>
-      <c r="T12" s="7">
+      <c r="T12" s="50">
         <v>4262484134</v>
       </c>
-      <c r="U12" s="7" t="s">
+      <c r="U12" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="V12" s="5" t="s">
+      <c r="V12" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" ht="16.5">
+      <c r="W12" s="52"/>
+      <c r="X12" s="52"/>
+      <c r="Y12" s="52"/>
+      <c r="Z12" s="52"/>
+      <c r="AA12" s="52"/>
+      <c r="AB12" s="52"/>
+      <c r="AC12" s="52"/>
+    </row>
+    <row r="13" spans="1:29" ht="16.5">
       <c r="A13" s="2">
         <v>3</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="50">
         <v>11815175044</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="9" t="s">
+      <c r="C13" s="2"/>
+      <c r="D13" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G13" s="2"/>
-      <c r="H13" s="48">
+      <c r="H13" s="11">
         <v>4</v>
       </c>
-      <c r="I13" s="48">
+      <c r="I13" s="11">
         <v>9</v>
       </c>
-      <c r="J13" s="45">
+      <c r="J13" s="8">
         <v>2018</v>
       </c>
-      <c r="K13" s="45" t="s">
+      <c r="K13" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="L13" s="49" t="s">
+      <c r="L13" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="M13" s="4"/>
-      <c r="N13" s="47">
+      <c r="M13" s="10"/>
+      <c r="N13" s="10">
         <v>14</v>
       </c>
-      <c r="O13" s="47">
+      <c r="O13" s="10">
         <v>14</v>
       </c>
-      <c r="P13" s="47">
+      <c r="P13" s="10">
         <v>37</v>
       </c>
-      <c r="Q13" s="52" t="s">
+      <c r="Q13" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="R13" s="52" t="s">
+      <c r="R13" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="S13" s="7">
+      <c r="S13" s="50">
         <v>15175044</v>
       </c>
-      <c r="T13" s="7">
+      <c r="T13" s="50">
         <v>4123804853</v>
       </c>
-      <c r="U13" s="11" t="s">
+      <c r="U13" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="V13" s="5" t="s">
+      <c r="V13" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" ht="16.5">
+      <c r="W13" s="52"/>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="52"/>
+      <c r="Z13" s="52"/>
+      <c r="AA13" s="52"/>
+      <c r="AB13" s="52"/>
+      <c r="AC13" s="52"/>
+    </row>
+    <row r="14" spans="1:29" ht="16.5">
       <c r="A14" s="2">
         <v>4</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="50">
         <v>11815756861</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="9" t="s">
+      <c r="C14" s="2"/>
+      <c r="D14" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="50" t="s">
         <v>62</v>
       </c>
       <c r="G14" s="2"/>
-      <c r="H14" s="48">
+      <c r="H14" s="11">
         <v>23</v>
       </c>
-      <c r="I14" s="48">
+      <c r="I14" s="11">
         <v>10</v>
       </c>
-      <c r="J14" s="45">
+      <c r="J14" s="8">
         <v>2018</v>
       </c>
-      <c r="K14" s="47" t="s">
+      <c r="K14" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="L14" s="47"/>
-      <c r="M14" s="47" t="s">
+      <c r="L14" s="10"/>
+      <c r="M14" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="N14" s="47">
+      <c r="N14" s="10">
         <v>12</v>
       </c>
-      <c r="O14" s="47">
+      <c r="O14" s="10">
         <v>12</v>
       </c>
-      <c r="P14" s="47">
+      <c r="P14" s="10">
         <v>35</v>
       </c>
-      <c r="Q14" s="52" t="s">
+      <c r="Q14" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="R14" s="53" t="s">
+      <c r="R14" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="S14" s="7">
+      <c r="S14" s="50">
         <v>15756861</v>
       </c>
-      <c r="T14" s="7">
+      <c r="T14" s="50">
         <v>4166768090</v>
       </c>
-      <c r="U14" s="7" t="s">
+      <c r="U14" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="V14" s="5" t="s">
+      <c r="V14" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" ht="16.5">
+      <c r="W14" s="52"/>
+      <c r="X14" s="52"/>
+      <c r="Y14" s="52"/>
+      <c r="Z14" s="52"/>
+      <c r="AA14" s="52"/>
+      <c r="AB14" s="52"/>
+      <c r="AC14" s="52"/>
+    </row>
+    <row r="15" spans="1:29" ht="28.5">
       <c r="A15" s="2">
         <v>5</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="50">
         <v>11819892696</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="9" t="s">
+      <c r="C15" s="2"/>
+      <c r="D15" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G15" s="2"/>
-      <c r="H15" s="48">
+      <c r="H15" s="11">
         <v>15</v>
       </c>
-      <c r="I15" s="48">
+      <c r="I15" s="11">
         <v>6</v>
       </c>
-      <c r="J15" s="45">
+      <c r="J15" s="8">
         <v>2018</v>
       </c>
-      <c r="K15" s="47" t="s">
+      <c r="K15" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="L15" s="47" t="s">
+      <c r="L15" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="M15" s="4"/>
-      <c r="N15" s="47">
+      <c r="M15" s="10"/>
+      <c r="N15" s="10">
         <v>12</v>
       </c>
-      <c r="O15" s="47">
+      <c r="O15" s="10">
         <v>12</v>
       </c>
-      <c r="P15" s="47">
+      <c r="P15" s="10">
         <v>34</v>
       </c>
-      <c r="Q15" s="54" t="s">
+      <c r="Q15" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="R15" s="52" t="s">
+      <c r="R15" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="S15" s="7">
+      <c r="S15" s="50">
         <v>19892696</v>
       </c>
-      <c r="T15" s="7">
+      <c r="T15" s="50">
         <v>4121206878</v>
       </c>
-      <c r="U15" s="7" t="s">
+      <c r="U15" s="50" t="s">
         <v>105</v>
       </c>
-      <c r="V15" s="5" t="s">
+      <c r="V15" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" ht="16.5">
+      <c r="W15" s="52"/>
+      <c r="X15" s="52"/>
+      <c r="Y15" s="52"/>
+      <c r="Z15" s="52"/>
+      <c r="AA15" s="52"/>
+      <c r="AB15" s="52"/>
+      <c r="AC15" s="52"/>
+    </row>
+    <row r="16" spans="1:29" ht="30">
       <c r="A16" s="2">
         <v>6</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="50">
         <v>11820198794</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="9" t="s">
+      <c r="C16" s="2"/>
+      <c r="D16" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="50" t="s">
         <v>62</v>
       </c>
       <c r="G16" s="2"/>
-      <c r="H16" s="48">
+      <c r="H16" s="11">
         <v>25</v>
       </c>
-      <c r="I16" s="48">
+      <c r="I16" s="11">
         <v>7</v>
       </c>
-      <c r="J16" s="45">
+      <c r="J16" s="8">
         <v>2018</v>
       </c>
-      <c r="K16" s="47" t="s">
+      <c r="K16" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="L16" s="47" t="s">
+      <c r="L16" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="M16" s="4"/>
-      <c r="N16" s="47">
+      <c r="M16" s="10"/>
+      <c r="N16" s="10">
         <v>10</v>
       </c>
-      <c r="O16" s="47">
+      <c r="O16" s="10">
         <v>10</v>
       </c>
-      <c r="P16" s="47">
+      <c r="P16" s="10">
         <v>35</v>
       </c>
-      <c r="Q16" s="54" t="s">
+      <c r="Q16" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="R16" s="52" t="s">
+      <c r="R16" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="S16" s="7">
+      <c r="S16" s="50">
         <v>20198794</v>
       </c>
-      <c r="T16" s="7">
+      <c r="T16" s="50">
         <v>4126057400</v>
       </c>
-      <c r="U16" s="7" t="s">
+      <c r="U16" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="V16" s="5" t="s">
+      <c r="V16" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="17" spans="1:22" ht="16.5">
+      <c r="W16" s="52"/>
+      <c r="X16" s="52"/>
+      <c r="Y16" s="52"/>
+      <c r="Z16" s="52"/>
+      <c r="AA16" s="52"/>
+      <c r="AB16" s="52"/>
+      <c r="AC16" s="52"/>
+    </row>
+    <row r="17" spans="1:29" ht="16.5">
       <c r="A17" s="2">
         <v>7</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="50">
         <v>11822655608</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="9" t="s">
+      <c r="C17" s="2"/>
+      <c r="D17" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G17" s="2"/>
-      <c r="H17" s="48">
+      <c r="H17" s="11">
         <v>29</v>
       </c>
-      <c r="I17" s="48">
+      <c r="I17" s="11">
         <v>11</v>
       </c>
-      <c r="J17" s="45">
+      <c r="J17" s="8">
         <v>2018</v>
       </c>
-      <c r="K17" s="47" t="s">
+      <c r="K17" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="L17" s="47" t="s">
+      <c r="L17" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="M17" s="4"/>
-      <c r="N17" s="47">
+      <c r="M17" s="10"/>
+      <c r="N17" s="10">
         <v>12</v>
       </c>
-      <c r="O17" s="47">
+      <c r="O17" s="10">
         <v>12</v>
       </c>
-      <c r="P17" s="47">
+      <c r="P17" s="10">
         <v>34</v>
       </c>
-      <c r="Q17" s="52" t="s">
+      <c r="Q17" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="R17" s="52" t="s">
+      <c r="R17" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="S17" s="7">
+      <c r="S17" s="50">
         <v>22655608</v>
       </c>
-      <c r="T17" s="7">
+      <c r="T17" s="50">
         <v>4121338291</v>
       </c>
-      <c r="U17" s="7" t="s">
+      <c r="U17" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="V17" s="5" t="s">
+      <c r="V17" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="18" spans="1:22" ht="16.5">
+      <c r="W17" s="52"/>
+      <c r="X17" s="52"/>
+      <c r="Y17" s="52"/>
+      <c r="Z17" s="52"/>
+      <c r="AA17" s="52"/>
+      <c r="AB17" s="52"/>
+      <c r="AC17" s="52"/>
+    </row>
+    <row r="18" spans="1:29" ht="16.5">
       <c r="A18" s="2">
         <v>8</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="50">
         <v>11823210437</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="9" t="s">
+      <c r="C18" s="2"/>
+      <c r="D18" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G18" s="2"/>
-      <c r="H18" s="48">
+      <c r="H18" s="11">
         <v>31</v>
       </c>
-      <c r="I18" s="48">
+      <c r="I18" s="11">
         <v>12</v>
       </c>
-      <c r="J18" s="45">
+      <c r="J18" s="8">
         <v>2018</v>
       </c>
-      <c r="K18" s="47" t="s">
+      <c r="K18" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="L18" s="47" t="s">
+      <c r="L18" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="M18" s="4"/>
-      <c r="N18" s="47">
+      <c r="M18" s="10"/>
+      <c r="N18" s="10">
         <v>10</v>
       </c>
-      <c r="O18" s="47">
+      <c r="O18" s="10">
         <v>10</v>
       </c>
-      <c r="P18" s="47">
+      <c r="P18" s="10">
         <v>33</v>
       </c>
-      <c r="Q18" s="53" t="s">
+      <c r="Q18" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="R18" s="53" t="s">
+      <c r="R18" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="S18" s="7">
+      <c r="S18" s="50">
         <v>23210437</v>
       </c>
-      <c r="T18" s="7">
+      <c r="T18" s="50">
         <v>4129351527</v>
       </c>
-      <c r="U18" s="7" t="s">
+      <c r="U18" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="V18" s="5" t="s">
+      <c r="V18" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="19" spans="1:22" ht="16.5">
+      <c r="W18" s="52"/>
+      <c r="X18" s="52"/>
+      <c r="Y18" s="52"/>
+      <c r="Z18" s="52"/>
+      <c r="AA18" s="52"/>
+      <c r="AB18" s="52"/>
+      <c r="AC18" s="52"/>
+    </row>
+    <row r="19" spans="1:29" ht="16.5">
       <c r="A19" s="2">
         <v>9</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="50">
         <v>11823717972</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="9" t="s">
+      <c r="C19" s="2"/>
+      <c r="D19" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G19" s="2"/>
-      <c r="H19" s="48">
+      <c r="H19" s="11">
         <v>23</v>
       </c>
-      <c r="I19" s="48">
+      <c r="I19" s="11">
         <v>9</v>
       </c>
-      <c r="J19" s="45">
+      <c r="J19" s="8">
         <v>2018</v>
       </c>
-      <c r="K19" s="47" t="s">
+      <c r="K19" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="L19" s="47" t="s">
+      <c r="L19" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="M19" s="4"/>
-      <c r="N19" s="47">
+      <c r="M19" s="10"/>
+      <c r="N19" s="10">
         <v>10</v>
       </c>
-      <c r="O19" s="47">
+      <c r="O19" s="10">
         <v>8</v>
       </c>
-      <c r="P19" s="47">
+      <c r="P19" s="10">
         <v>35</v>
       </c>
-      <c r="Q19" s="52" t="s">
+      <c r="Q19" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="R19" s="52" t="s">
+      <c r="R19" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="S19" s="7">
+      <c r="S19" s="50">
         <v>23717972</v>
       </c>
-      <c r="T19" s="7">
+      <c r="T19" s="50">
         <v>4121210168</v>
       </c>
-      <c r="U19" s="7" t="s">
+      <c r="U19" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="V19" s="5" t="s">
+      <c r="V19" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="20" spans="1:22" ht="16.5">
+      <c r="W19" s="52"/>
+      <c r="X19" s="52"/>
+      <c r="Y19" s="52"/>
+      <c r="Z19" s="52"/>
+      <c r="AA19" s="52"/>
+      <c r="AB19" s="52"/>
+      <c r="AC19" s="52"/>
+    </row>
+    <row r="20" spans="1:29" ht="16.5">
       <c r="A20" s="2">
         <v>10</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="50">
         <v>11823723978</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="9" t="s">
+      <c r="C20" s="2"/>
+      <c r="D20" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="50" t="s">
         <v>64</v>
       </c>
       <c r="G20" s="2"/>
-      <c r="H20" s="48">
+      <c r="H20" s="11">
         <v>13</v>
       </c>
-      <c r="I20" s="48">
+      <c r="I20" s="11">
         <v>2</v>
       </c>
-      <c r="J20" s="45">
+      <c r="J20" s="8">
         <v>2018</v>
       </c>
-      <c r="K20" s="47" t="s">
+      <c r="K20" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="L20" s="47" t="s">
+      <c r="L20" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="M20" s="4"/>
-      <c r="N20" s="47">
+      <c r="M20" s="10"/>
+      <c r="N20" s="10">
         <v>10</v>
       </c>
-      <c r="O20" s="47">
+      <c r="O20" s="10">
         <v>10</v>
       </c>
-      <c r="P20" s="47">
+      <c r="P20" s="10">
         <v>33</v>
       </c>
-      <c r="Q20" s="52" t="s">
+      <c r="Q20" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="R20" s="52" t="s">
+      <c r="R20" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="S20" s="7">
+      <c r="S20" s="50">
         <v>23723978</v>
       </c>
-      <c r="T20" s="7">
+      <c r="T20" s="50">
         <v>4125097458</v>
       </c>
-      <c r="U20" s="7" t="s">
+      <c r="U20" s="50" t="s">
         <v>109</v>
       </c>
-      <c r="V20" s="5" t="s">
+      <c r="V20" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="21" spans="1:22" ht="16.5">
+      <c r="W20" s="52"/>
+      <c r="X20" s="52"/>
+      <c r="Y20" s="52"/>
+      <c r="Z20" s="52"/>
+      <c r="AA20" s="52"/>
+      <c r="AB20" s="52"/>
+      <c r="AC20" s="52"/>
+    </row>
+    <row r="21" spans="1:29" ht="16.5">
       <c r="A21" s="2">
         <v>11</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="50">
         <v>11824198274</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="9" t="s">
+      <c r="C21" s="2"/>
+      <c r="D21" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G21" s="2"/>
-      <c r="H21" s="48">
+      <c r="H21" s="11">
         <v>13</v>
       </c>
-      <c r="I21" s="48">
+      <c r="I21" s="11">
         <v>12</v>
       </c>
-      <c r="J21" s="45">
+      <c r="J21" s="8">
         <v>2018</v>
       </c>
-      <c r="K21" s="47" t="s">
+      <c r="K21" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="L21" s="47" t="s">
+      <c r="L21" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="M21" s="4"/>
-      <c r="N21" s="47">
+      <c r="M21" s="10"/>
+      <c r="N21" s="10">
         <v>10</v>
       </c>
-      <c r="O21" s="47">
+      <c r="O21" s="10">
         <v>10</v>
       </c>
-      <c r="P21" s="47">
+      <c r="P21" s="10">
         <v>33</v>
       </c>
-      <c r="Q21" s="52" t="s">
+      <c r="Q21" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="R21" s="52" t="s">
+      <c r="R21" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="S21" s="7">
+      <c r="S21" s="50">
         <v>24198274</v>
       </c>
-      <c r="T21" s="7">
+      <c r="T21" s="50">
         <v>4129542916</v>
       </c>
-      <c r="U21" s="7" t="s">
+      <c r="U21" s="50" t="s">
         <v>110</v>
       </c>
-      <c r="V21" s="5" t="s">
+      <c r="V21" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="22" spans="1:22" ht="16.5">
+      <c r="W21" s="52"/>
+      <c r="X21" s="52"/>
+      <c r="Y21" s="52"/>
+      <c r="Z21" s="52"/>
+      <c r="AA21" s="52"/>
+      <c r="AB21" s="52"/>
+      <c r="AC21" s="52"/>
+    </row>
+    <row r="22" spans="1:29" ht="16.5">
       <c r="A22" s="2">
         <v>12</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="50">
         <v>11825560233</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="9" t="s">
+      <c r="C22" s="2"/>
+      <c r="D22" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="50" t="s">
         <v>62</v>
       </c>
       <c r="G22" s="2"/>
-      <c r="H22" s="48">
+      <c r="H22" s="11">
         <v>27</v>
       </c>
-      <c r="I22" s="48">
+      <c r="I22" s="11">
         <v>11</v>
       </c>
-      <c r="J22" s="45">
+      <c r="J22" s="8">
         <v>2018</v>
       </c>
-      <c r="K22" s="47" t="s">
+      <c r="K22" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="L22" s="47" t="s">
+      <c r="L22" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="M22" s="4"/>
-      <c r="N22" s="47">
+      <c r="M22" s="10"/>
+      <c r="N22" s="10">
         <v>12</v>
       </c>
-      <c r="O22" s="47">
+      <c r="O22" s="10">
         <v>12</v>
       </c>
-      <c r="P22" s="47">
+      <c r="P22" s="10">
         <v>33</v>
       </c>
-      <c r="Q22" s="52" t="s">
+      <c r="Q22" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="R22" s="52" t="s">
+      <c r="R22" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="S22" s="7">
+      <c r="S22" s="50">
         <v>25560233</v>
       </c>
-      <c r="T22" s="7">
+      <c r="T22" s="50">
         <v>4122542430</v>
       </c>
-      <c r="U22" s="7" t="s">
+      <c r="U22" s="50" t="s">
         <v>111</v>
       </c>
-      <c r="V22" s="5" t="s">
+      <c r="V22" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="23" spans="1:22" ht="16.5">
+      <c r="W22" s="52"/>
+      <c r="X22" s="52"/>
+      <c r="Y22" s="52"/>
+      <c r="Z22" s="52"/>
+      <c r="AA22" s="52"/>
+      <c r="AB22" s="52"/>
+      <c r="AC22" s="52"/>
+    </row>
+    <row r="23" spans="1:29" ht="16.5">
       <c r="A23" s="2">
         <v>13</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="50">
         <v>11826128520</v>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="9" t="s">
+      <c r="C23" s="2"/>
+      <c r="D23" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G23" s="2"/>
-      <c r="H23" s="48">
+      <c r="H23" s="11">
         <v>15</v>
       </c>
-      <c r="I23" s="48">
+      <c r="I23" s="11">
         <v>3</v>
       </c>
-      <c r="J23" s="45">
+      <c r="J23" s="8">
         <v>2018</v>
       </c>
-      <c r="K23" s="47" t="s">
+      <c r="K23" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="L23" s="47" t="s">
+      <c r="L23" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="M23" s="4"/>
-      <c r="N23" s="47">
+      <c r="M23" s="10"/>
+      <c r="N23" s="10">
         <v>12</v>
       </c>
-      <c r="O23" s="47">
+      <c r="O23" s="10">
         <v>12</v>
       </c>
-      <c r="P23" s="47">
+      <c r="P23" s="10">
         <v>35</v>
       </c>
-      <c r="Q23" s="52" t="s">
+      <c r="Q23" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="R23" s="52" t="s">
+      <c r="R23" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="S23" s="7">
+      <c r="S23" s="50">
         <v>26128520</v>
       </c>
-      <c r="T23" s="7">
+      <c r="T23" s="50">
         <v>4127646372</v>
       </c>
-      <c r="U23" s="7" t="s">
+      <c r="U23" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="V23" s="5" t="s">
+      <c r="V23" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="24" spans="1:22" ht="16.5">
+      <c r="W23" s="52"/>
+      <c r="X23" s="52"/>
+      <c r="Y23" s="52"/>
+      <c r="Z23" s="52"/>
+      <c r="AA23" s="52"/>
+      <c r="AB23" s="52"/>
+      <c r="AC23" s="52"/>
+    </row>
+    <row r="24" spans="1:29" ht="16.5">
       <c r="A24" s="2">
         <v>14</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="50">
         <v>11826587738</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="9" t="s">
+      <c r="C24" s="2"/>
+      <c r="D24" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G24" s="2"/>
-      <c r="H24" s="48">
+      <c r="H24" s="11">
         <v>25</v>
       </c>
-      <c r="I24" s="50" t="s">
+      <c r="I24" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="J24" s="45">
+      <c r="J24" s="8">
         <v>2018</v>
       </c>
-      <c r="K24" s="47" t="s">
+      <c r="K24" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="L24" s="47" t="s">
+      <c r="L24" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="M24" s="4"/>
-      <c r="N24" s="47">
+      <c r="M24" s="10"/>
+      <c r="N24" s="10">
         <v>12</v>
       </c>
-      <c r="O24" s="47">
+      <c r="O24" s="10">
         <v>12</v>
       </c>
-      <c r="P24" s="47">
+      <c r="P24" s="10">
         <v>35</v>
       </c>
-      <c r="Q24" s="52" t="s">
+      <c r="Q24" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="R24" s="52" t="s">
+      <c r="R24" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="S24" s="7">
+      <c r="S24" s="50">
         <v>26587738</v>
       </c>
-      <c r="T24" s="7">
+      <c r="T24" s="50">
         <v>4126390525</v>
       </c>
-      <c r="U24" s="7" t="s">
+      <c r="U24" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="V24" s="5" t="s">
+      <c r="V24" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="25" spans="1:22" ht="16.5">
+      <c r="W24" s="52"/>
+      <c r="X24" s="52"/>
+      <c r="Y24" s="52"/>
+      <c r="Z24" s="52"/>
+      <c r="AA24" s="52"/>
+      <c r="AB24" s="52"/>
+      <c r="AC24" s="52"/>
+    </row>
+    <row r="25" spans="1:29" ht="16.5">
       <c r="A25" s="2">
         <v>15</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="50">
         <v>11827229244</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="9" t="s">
+      <c r="C25" s="2"/>
+      <c r="D25" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="50" t="s">
         <v>62</v>
       </c>
       <c r="G25" s="2"/>
-      <c r="H25" s="51">
+      <c r="H25" s="14">
         <v>22</v>
       </c>
-      <c r="I25" s="51">
+      <c r="I25" s="14">
         <v>10</v>
       </c>
-      <c r="J25" s="45">
+      <c r="J25" s="8">
         <v>2018</v>
       </c>
-      <c r="K25" s="47" t="s">
+      <c r="K25" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="L25" s="47" t="s">
+      <c r="L25" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="M25" s="4"/>
-      <c r="N25" s="47">
+      <c r="M25" s="10"/>
+      <c r="N25" s="10">
         <v>8</v>
       </c>
-      <c r="O25" s="47">
+      <c r="O25" s="10">
         <v>8</v>
       </c>
-      <c r="P25" s="47">
+      <c r="P25" s="10">
         <v>35</v>
       </c>
-      <c r="Q25" s="52" t="s">
+      <c r="Q25" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="R25" s="52" t="s">
+      <c r="R25" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="S25" s="7">
+      <c r="S25" s="50">
         <v>27229244</v>
       </c>
-      <c r="T25" s="7">
+      <c r="T25" s="50">
         <v>4268859857</v>
       </c>
-      <c r="U25" s="12" t="s">
+      <c r="U25" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="V25" s="5" t="s">
+      <c r="V25" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="26" spans="1:22" ht="16.5">
+      <c r="W25" s="52"/>
+      <c r="X25" s="52"/>
+      <c r="Y25" s="52"/>
+      <c r="Z25" s="52"/>
+      <c r="AA25" s="52"/>
+      <c r="AB25" s="52"/>
+      <c r="AC25" s="52"/>
+    </row>
+    <row r="26" spans="1:29" ht="16.5">
       <c r="A26" s="2">
         <v>16</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="50">
         <v>11923583989</v>
       </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="9" t="s">
+      <c r="C26" s="2"/>
+      <c r="D26" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="50" t="s">
         <v>62</v>
       </c>
       <c r="G26" s="2"/>
-      <c r="H26" s="48">
+      <c r="H26" s="11">
         <v>15</v>
       </c>
-      <c r="I26" s="48">
+      <c r="I26" s="11">
         <v>9</v>
       </c>
-      <c r="J26" s="45">
+      <c r="J26" s="8">
         <v>2018</v>
       </c>
-      <c r="K26" s="47" t="s">
+      <c r="K26" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="L26" s="47" t="s">
+      <c r="L26" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="M26" s="4"/>
-      <c r="N26" s="47">
+      <c r="M26" s="10"/>
+      <c r="N26" s="10">
         <v>10</v>
       </c>
-      <c r="O26" s="47">
+      <c r="O26" s="10">
         <v>10</v>
       </c>
-      <c r="P26" s="47">
+      <c r="P26" s="10">
         <v>33</v>
       </c>
-      <c r="Q26" s="52" t="s">
+      <c r="Q26" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="R26" s="52" t="s">
+      <c r="R26" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="S26" s="7">
+      <c r="S26" s="50">
         <v>23583989</v>
       </c>
-      <c r="T26" s="7">
+      <c r="T26" s="50">
         <v>4161303179</v>
       </c>
-      <c r="U26" s="7" t="s">
+      <c r="U26" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="V26" s="5" t="s">
+      <c r="V26" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="27" spans="1:22" ht="17.25" thickBot="1">
+      <c r="W26" s="52"/>
+      <c r="X26" s="52"/>
+      <c r="Y26" s="52"/>
+      <c r="Z26" s="52"/>
+      <c r="AA26" s="52"/>
+      <c r="AB26" s="52"/>
+      <c r="AC26" s="52"/>
+    </row>
+    <row r="27" spans="1:29" ht="17.25" thickBot="1">
       <c r="A27" s="2">
         <v>17</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="53">
         <v>11928163553</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="10" t="s">
+      <c r="C27" s="2"/>
+      <c r="D27" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="53" t="s">
         <v>63</v>
       </c>
       <c r="G27" s="2"/>
-      <c r="H27" s="48">
+      <c r="H27" s="11">
         <v>23</v>
       </c>
-      <c r="I27" s="48">
+      <c r="I27" s="11">
         <v>8</v>
       </c>
-      <c r="J27" s="45">
+      <c r="J27" s="8">
         <v>2018</v>
       </c>
-      <c r="K27" s="47" t="s">
+      <c r="K27" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="L27" s="47" t="s">
+      <c r="L27" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="M27" s="4"/>
-      <c r="N27" s="47">
+      <c r="M27" s="10"/>
+      <c r="N27" s="10">
         <v>12</v>
       </c>
-      <c r="O27" s="47">
+      <c r="O27" s="10">
         <v>12</v>
       </c>
-      <c r="P27" s="47">
+      <c r="P27" s="10">
         <v>34</v>
       </c>
-      <c r="Q27" s="52" t="s">
+      <c r="Q27" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="R27" s="52" t="s">
+      <c r="R27" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="S27" s="8">
+      <c r="S27" s="53">
         <v>28163553</v>
       </c>
-      <c r="T27" s="8">
+      <c r="T27" s="53">
         <v>4126031627</v>
       </c>
-      <c r="U27" s="8" t="s">
+      <c r="U27" s="53" t="s">
         <v>115</v>
       </c>
-      <c r="V27" s="5" t="s">
+      <c r="V27" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="32" spans="1:22">
-      <c r="T32" s="55"/>
+      <c r="W27" s="52"/>
+      <c r="X27" s="52"/>
+      <c r="Y27" s="52"/>
+      <c r="Z27" s="52"/>
+      <c r="AA27" s="52"/>
+      <c r="AB27" s="52"/>
+      <c r="AC27" s="52"/>
+    </row>
+    <row r="28" spans="1:29">
+      <c r="A28" s="52"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="52"/>
+      <c r="K28" s="52"/>
+      <c r="L28" s="52"/>
+      <c r="M28" s="52"/>
+      <c r="N28" s="52"/>
+      <c r="O28" s="52"/>
+      <c r="P28" s="52"/>
+      <c r="Q28" s="52"/>
+      <c r="R28" s="52"/>
+      <c r="S28" s="52"/>
+      <c r="T28" s="52"/>
+      <c r="U28" s="52"/>
+      <c r="V28" s="52"/>
+      <c r="W28" s="52"/>
+      <c r="X28" s="52"/>
+      <c r="Y28" s="52"/>
+      <c r="Z28" s="52"/>
+      <c r="AA28" s="52"/>
+      <c r="AB28" s="52"/>
+      <c r="AC28" s="52"/>
+    </row>
+    <row r="29" spans="1:29">
+      <c r="A29" s="52"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="52"/>
+      <c r="J29" s="52"/>
+      <c r="K29" s="52"/>
+      <c r="L29" s="52"/>
+      <c r="M29" s="52"/>
+      <c r="N29" s="52"/>
+      <c r="O29" s="52"/>
+      <c r="P29" s="52"/>
+      <c r="Q29" s="52"/>
+      <c r="R29" s="52"/>
+      <c r="S29" s="52"/>
+      <c r="T29" s="52"/>
+      <c r="U29" s="52"/>
+      <c r="V29" s="52"/>
+      <c r="W29" s="52"/>
+      <c r="X29" s="52"/>
+      <c r="Y29" s="52"/>
+      <c r="Z29" s="52"/>
+      <c r="AA29" s="52"/>
+      <c r="AB29" s="52"/>
+      <c r="AC29" s="52"/>
+    </row>
+    <row r="30" spans="1:29">
+      <c r="A30" s="52"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
+      <c r="L30" s="52"/>
+      <c r="M30" s="52"/>
+      <c r="N30" s="52"/>
+      <c r="O30" s="52"/>
+      <c r="P30" s="52"/>
+      <c r="Q30" s="52"/>
+      <c r="R30" s="52"/>
+      <c r="S30" s="52"/>
+      <c r="T30" s="52"/>
+      <c r="U30" s="52"/>
+      <c r="V30" s="52"/>
+      <c r="W30" s="52"/>
+      <c r="X30" s="52"/>
+      <c r="Y30" s="52"/>
+      <c r="Z30" s="52"/>
+      <c r="AA30" s="52"/>
+      <c r="AB30" s="52"/>
+      <c r="AC30" s="52"/>
+    </row>
+    <row r="31" spans="1:29">
+      <c r="A31" s="52"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="52"/>
+      <c r="K31" s="52"/>
+      <c r="L31" s="52"/>
+      <c r="M31" s="52"/>
+      <c r="N31" s="52"/>
+      <c r="O31" s="52"/>
+      <c r="P31" s="52"/>
+      <c r="Q31" s="52"/>
+      <c r="R31" s="52"/>
+      <c r="S31" s="52"/>
+      <c r="T31" s="52"/>
+      <c r="U31" s="52"/>
+      <c r="V31" s="52"/>
+      <c r="W31" s="52"/>
+      <c r="X31" s="52"/>
+      <c r="Y31" s="52"/>
+      <c r="Z31" s="52"/>
+      <c r="AA31" s="52"/>
+      <c r="AB31" s="52"/>
+      <c r="AC31" s="52"/>
+    </row>
+    <row r="32" spans="1:29">
+      <c r="A32" s="52"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="52"/>
+      <c r="M32" s="52"/>
+      <c r="N32" s="52"/>
+      <c r="O32" s="52"/>
+      <c r="P32" s="52"/>
+      <c r="Q32" s="52"/>
+      <c r="R32" s="52"/>
+      <c r="S32" s="52"/>
+      <c r="T32" s="18"/>
+      <c r="U32" s="52"/>
+      <c r="V32" s="52"/>
+      <c r="W32" s="52"/>
+      <c r="X32" s="52"/>
+      <c r="Y32" s="52"/>
+      <c r="Z32" s="52"/>
+      <c r="AA32" s="52"/>
+      <c r="AB32" s="52"/>
+      <c r="AC32" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="Q9:R10"/>
-    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="A5:V5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="M6:P6"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="S6:V6"/>
     <mergeCell ref="O7:R7"/>
     <mergeCell ref="U7:V7"/>
     <mergeCell ref="A8:P8"/>
@@ -2591,14 +2855,15 @@
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="M7:N7"/>
-    <mergeCell ref="A5:V5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="M6:P6"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="Q9:R10"/>
+    <mergeCell ref="S9:S10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
